--- a/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:17</t>
+          <t>2026-09-29 01:02:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:19</t>
+          <t>2026-09-29 01:02:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:20</t>
+          <t>2026-09-29 01:02:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.75%1,034,000</t>
+          <t>8.91%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.91%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.99%442,000</t>
+          <t>7.06%413,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>7.06%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>442000</v>
+        <v>413000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.23%221,000</t>
+          <t>5.30%221,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8525</v>
+        <v>1165</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.04%173,000</t>
+          <t>4.90%1,209,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>173000</v>
+        <v>1209000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1185</v>
+        <v>3400</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.90%1,209,000</t>
+          <t>4.46%377,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1209000</v>
+        <v>377000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3555</v>
+        <v>5185</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.58%377,000</t>
+          <t>4.29%238,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>377000</v>
+        <v>238000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5415</v>
+        <v>7925</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.41%238,000</t>
+          <t>4.27%155,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.27%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>238000</v>
+        <v>155000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.92%227,000</t>
+          <t>3.89%227,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.91%598,000</t>
+          <t>3.82%598,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.69%470,000</t>
+          <t>3.57%470,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19835</v>
+        <v>2100</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.21%47,400</t>
+          <t>3.20%438,197</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>47400</v>
+        <v>438197</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2115</v>
+        <v>19395</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.17%438,197</t>
+          <t>3.20%47,400</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>438197</v>
+        <v>47400</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.95%3,627,000</t>
+          <t>3.12%3,627,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:05</t>
+          <t>2026-09-29 22:56:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1195</v>
+        <v>1310</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%596,000</t>
+          <t>2.72%596,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>948</v>
+        <v>2445</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.02%622,000</t>
+          <t>2.05%241,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>622000</v>
+        <v>241000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2340</v>
+        <v>945</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.93%241,000</t>
+          <t>2.05%622,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>241000</v>
+        <v>622000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.92%538</t>
+          <t>+8.14%94.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+8.14%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>538</v>
+        <v>94.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%1,034,000</t>
+          <t>2.02%6,147,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1034000</v>
+        <v>6147000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.96%150</t>
+          <t>-3.16%521</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>150</v>
+        <v>521</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.59%3,104,000</t>
+          <t>1.87%1,034,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3104000</v>
+        <v>1034000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.49%207</t>
+          <t>+1%151.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>207</v>
+        <v>151.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.56%2,208,000</t>
+          <t>1.64%3,104,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2208000</v>
+        <v>3104000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,34 +1724,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>+0.24%207.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1895</v>
+        <v>207.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.47%227,000</t>
+          <t>1.59%2,208,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>227000</v>
+        <v>2208000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.11%87.2</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>87.2</v>
+        <v>3305</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.46%4,903,000</t>
+          <t>1.52%132,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4903000</v>
+        <v>132000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3230</v>
+        <v>1120</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.46%132,000</t>
+          <t>1.47%378,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>132000</v>
+        <v>378000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1105</v>
+        <v>1810</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.43%378,000</t>
+          <t>1.43%227,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>378000</v>
+        <v>227000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.47%810</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.47%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>810</v>
+        <v>153.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.12%404,000</t>
+          <t>1.12%2,096,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>404000</v>
+        <v>2096000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.73%796</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>699</v>
+        <v>796</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.11%464,000</t>
+          <t>1.12%404,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>464000</v>
+        <v>404000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>154</v>
+        <v>687</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.10%2,096,000</t>
+          <t>1.11%464,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2096000</v>
+        <v>464000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>311</v>
+        <v>294.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.06%999,000</t>
+          <t>1.02%999,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%243</t>
+          <t>-2.06%238</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:06</t>
+          <t>2026-09-29 22:56:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.67%222.5</t>
+          <t>+1.57%226</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>222.5</v>
+        <v>226</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.84%1,107,336</t>
+          <t>0.87%1,107,336</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6245</v>
+        <v>250.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.83%39,000</t>
+          <t>0.84%960,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>39000</v>
+        <v>960000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>-0.51%1960</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>250.5</v>
+        <v>1960</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.82%960,000</t>
+          <t>0.83%122,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>960000</v>
+        <v>122000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.03%1970</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1970</v>
+        <v>6020</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.82%122,000</t>
+          <t>0.82%39,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>122000</v>
+        <v>39000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.87%449</t>
+          <t>+1.34%455</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.52%340,000</t>
+          <t>0.54%340,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3167大量</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+6.63%949</t>
+          <t>-0.37%540</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+6.63%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>949</v>
+        <v>540</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.37%115,000</t>
+          <t>0.38%200,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>3167大量</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%542</t>
+          <t>-4.85%903</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>542</v>
+        <v>903</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%200,000</t>
+          <t>0.36%115,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>200000</v>
+        <v>115000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.39%761</t>
+          <t>+2.37%779</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.35%133,000</t>
+          <t>0.36%133,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%165</t>
+          <t>-2.42%161</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.99%1530</t>
+          <t>-1.96%1500</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0%100.5</t>
+          <t>-5.47%95</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>100.5</v>
+        <v>95</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.29%834,000</t>
+          <t>0.28%834,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.22%229</t>
+          <t>-0.87%227</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.13%376</t>
+          <t>+0.93%379.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>376</v>
+        <v>379.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.23%178,000</t>
+          <t>0.24%178,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5670</v>
+        <v>5585</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:41:08</t>
+          <t>2026-09-29 22:56:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.4%124.5</t>
+          <t>0%124.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:43</t>
+          <t>2026-09-29 23:07:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:44</t>
+          <t>2026-09-29 23:07:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:45</t>
+          <t>2026-09-29 23:07:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:40</t>
+          <t>2026-09-29 23:52:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:41</t>
+          <t>2026-09-29 23:52:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:43</t>
+          <t>2026-09-29 23:52:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
